--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486447_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486447_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8791</v>
+        <v>2.0837</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4661</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4131</v>
+        <v>1.4965</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.5694</v>
+        <v>1.0128</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.076</v>
+        <v>0.6965</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4933</v>
+        <v>0.3163</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.07820000000000001</v>
+        <v>1.703</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5903</v>
+        <v>2.0074</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6686</v>
+        <v>-0.3044</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4911</v>
+        <v>-0.6902</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6663</v>
+        <v>-1.3109</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8248</v>
+        <v>0.6207</v>
       </c>
       <c r="P2" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3117</v>
+        <v>-0.5588</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6934</v>
+        <v>-0.4182</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3816</v>
+        <v>-0.1406</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4552</v>
+        <v>2.0647</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4552</v>
+        <v>1.695</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5019</v>
+        <v>2.0479</v>
       </c>
       <c r="E3" t="n">
-        <v>0.252</v>
+        <v>1.7581</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2499</v>
+        <v>0.2898</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0128</v>
+        <v>-1.5694</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6965</v>
+        <v>-0.076</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3163</v>
+        <v>-1.4933</v>
       </c>
       <c r="J3" t="n">
-        <v>1.703</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0074</v>
+        <v>0.5903</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3044</v>
+        <v>-0.6686</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6902</v>
+        <v>-1.4911</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3109</v>
+        <v>-0.6663</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6207</v>
+        <v>-0.8248</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1407</v>
+        <v>-0.143</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4014</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3872</v>
+        <v>0.2584</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0647</v>
+        <v>2.4552</v>
       </c>
       <c r="W3" t="n">
-        <v>1.695</v>
+        <v>2.4552</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8247</v>
+        <v>-0.412</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5776</v>
+        <v>-0.0987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2471</v>
+        <v>-0.3132</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.9899</v>
+        <v>-0.2287</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6487</v>
+        <v>-0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.3412</v>
+        <v>-0.1952</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.5498</v>
+        <v>0.0382</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3529</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.1969</v>
+        <v>0.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4401</v>
+        <v>-0.267</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2959</v>
+        <v>-0.0335</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1443</v>
+        <v>-0.2335</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6101</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7743</v>
+        <v>-0.1833</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0022</v>
+        <v>-0.137</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7721</v>
+        <v>-0.0463</v>
       </c>
       <c r="V4" t="n">
-        <v>4.9103</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>6.6053</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4736</v>
+        <v>-0.5317</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0987</v>
+        <v>-0.3164</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3749</v>
+        <v>-0.2153</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2287</v>
+        <v>-4.9899</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0335</v>
+        <v>-2.6487</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1952</v>
+        <v>-2.3412</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0382</v>
+        <v>-3.5498</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-1.3529</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0382</v>
+        <v>-2.1969</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.267</v>
+        <v>-1.4401</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0335</v>
+        <v>-1.2959</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2335</v>
+        <v>-0.1443</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.6101</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2449</v>
+        <v>0.4179</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.137</v>
+        <v>0.1082</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1079</v>
+        <v>0.3097</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.9103</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>6.6053</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1309</v>
+        <v>-1.1001</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2055</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9254</v>
+        <v>-0.8946</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4495</v>
@@ -922,13 +922,13 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.334</v>
+        <v>-0.3031</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5649999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2619</v>
+        <v>-1.3544</v>
       </c>
       <c r="E7" t="n">
         <v>-1.7458</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4839</v>
+        <v>0.3914</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4743</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4402</v>
+        <v>-0.5327</v>
       </c>
       <c r="T7" t="n">
         <v>-0.274</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1662</v>
+        <v>-0.2587</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2848</v>
+        <v>-2.2286</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4436</v>
+        <v>-0.3809</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1588</v>
+        <v>-1.8477</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7398</v>
+        <v>-1.9851</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4387</v>
+        <v>-0.2982</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6988</v>
+        <v>-1.687</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6521</v>
+        <v>0.0646</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0547</v>
+        <v>0.7331</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7068</v>
+        <v>-0.6686</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0878</v>
+        <v>-2.0497</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4934</v>
+        <v>-1.0313</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4056</v>
+        <v>-1.0184</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.435</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4574</v>
+        <v>-0.548</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6165</v>
+        <v>-0.4879</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1591</v>
+        <v>-0.0601</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4204</v>
+        <v>-2.2383</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4493</v>
+        <v>-2.6834</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.971</v>
+        <v>0.4451</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9851</v>
+        <v>-1.6855</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2982</v>
+        <v>-0.8942</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.687</v>
+        <v>-0.7913</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0646</v>
+        <v>-1.4336</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7331</v>
+        <v>0.0182</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6686</v>
+        <v>-1.4519</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0497</v>
+        <v>-0.2519</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0313</v>
+        <v>-0.9125</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0184</v>
+        <v>0.6606</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7398</v>
+        <v>-0.5528</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5564</v>
+        <v>-0.1622</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1834</v>
+        <v>-0.3906</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4733</v>
+        <v>-2.2462</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7951</v>
+        <v>-3.2201</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3218</v>
+        <v>0.9739</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6855</v>
+        <v>-0.7398</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8942</v>
+        <v>-1.4387</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7913</v>
+        <v>0.6988</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4336</v>
+        <v>-0.6521</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0182</v>
+        <v>0.0547</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4519</v>
+        <v>-0.7068</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2519</v>
+        <v>-0.0878</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9125</v>
+        <v>-1.4934</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6606</v>
+        <v>1.4056</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.4188</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>-0.3929</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5138</v>
+        <v>-0.0258</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.621</v>
+        <v>-2.3708</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.468</v>
+        <v>-2.8007</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.153</v>
+        <v>0.4298</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.1178</v>
+        <v>-4.3211</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.281</v>
+        <v>-4.1179</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8368</v>
+        <v>-0.2032</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4322</v>
+        <v>-2.547</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2497</v>
+        <v>-2.7216</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1825</v>
+        <v>0.1745</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6856</v>
+        <v>-1.7741</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0313</v>
+        <v>-1.3963</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6543</v>
+        <v>-0.3778</v>
       </c>
       <c r="P11" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0618</v>
+        <v>0.0373</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0517</v>
+        <v>-0.4266</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0101</v>
+        <v>0.4638</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7746</v>
+        <v>-2.8763</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2044</v>
+        <v>-1.8466</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4298</v>
+        <v>-1.0297</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3211</v>
+        <v>-5.1178</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.1179</v>
+        <v>-2.281</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2032</v>
+        <v>-2.8368</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.547</v>
+        <v>-2.4322</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.7216</v>
+        <v>-1.2497</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1745</v>
+        <v>-1.1825</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7741</v>
+        <v>-2.6856</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3963</v>
+        <v>-1.0313</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3778</v>
+        <v>-1.6543</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3665</v>
+        <v>-0.1935</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8304</v>
+        <v>-0.3268</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4638</v>
+        <v>0.1334</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8248</v>
+        <v>-5.4904</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9512</v>
+        <v>-3.7709</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8736</v>
+        <v>-1.7195</v>
       </c>
       <c r="G13" t="n">
         <v>-3.7765</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9608</v>
+        <v>-0.6264</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5047</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2758</v>
+        <v>-0.1217</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.0596</v>
+        <v>-16.7172</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.0659</v>
+        <v>-14.7237</v>
       </c>
       <c r="F14" t="n">
         <v>-1.9935</v>
@@ -1522,10 +1522,10 @@
         <v>-12.5377</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.609299999999999</v>
+        <v>-5.6093</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.9288</v>
+        <v>-6.928800000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-12.7872</v>
@@ -1546,13 +1546,13 @@
         <v>13.0503</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.9477</v>
+        <v>-3.6052</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.9718</v>
+        <v>-3.629</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02390000000000009</v>
+        <v>0.02390000000000003</v>
       </c>
       <c r="V14" t="n">
         <v>11.1251</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7427</v>
+        <v>10.7504</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0017</v>
+        <v>7.2252</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7409</v>
+        <v>3.5252</v>
       </c>
       <c r="G15" t="n">
         <v>7.542</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8956</v>
+        <v>0.9034</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3389</v>
+        <v>-0.1153</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2345</v>
+        <v>1.0187</v>
       </c>
       <c r="V15" t="n">
         <v>0.5649999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8392</v>
+        <v>6.3248</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6564</v>
+        <v>0.0142</v>
       </c>
       <c r="F16" t="n">
-        <v>6.4955</v>
+        <v>6.3106</v>
       </c>
       <c r="G16" t="n">
         <v>4.6425</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4129</v>
+        <v>0.0727</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2209</v>
+        <v>-0.5504</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.6231</v>
       </c>
       <c r="V16" t="n">
         <v>0.7395</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>T. MCFADDEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1327</v>
+        <v>3.5389</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4908</v>
+        <v>1.4631</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6419</v>
+        <v>2.0757</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3407</v>
+        <v>3.3909</v>
       </c>
       <c r="H17" t="n">
-        <v>1.834</v>
+        <v>2.3692</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4933</v>
+        <v>1.0216</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3001</v>
+        <v>3.3496</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0069</v>
+        <v>2.5216</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7068</v>
+        <v>0.828</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0407</v>
+        <v>0.0413</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.1523</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2136</v>
+        <v>0.1936</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4869</v>
+        <v>-0.1995</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1907</v>
+        <v>-0.2764</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2962</v>
+        <v>0.0769</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. MCFADDEN</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6217</v>
+        <v>2.7219</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7926</v>
+        <v>1.7947</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8292</v>
+        <v>0.9272</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3909</v>
+        <v>4.6764</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3692</v>
+        <v>3.1632</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0216</v>
+        <v>1.5133</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3496</v>
+        <v>2.6932</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5216</v>
+        <v>2.2875</v>
       </c>
       <c r="L18" t="n">
-        <v>0.828</v>
+        <v>0.4057</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0413</v>
+        <v>1.9833</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1523</v>
+        <v>0.8757</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1936</v>
+        <v>1.1076</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1166</v>
+        <v>0.6757</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9469</v>
+        <v>0.1466</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1697</v>
+        <v>0.529</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4657</v>
+        <v>2.0575</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1241</v>
+        <v>1.2614</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3415</v>
+        <v>0.796</v>
       </c>
       <c r="G19" t="n">
-        <v>4.6764</v>
+        <v>1.3407</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1632</v>
+        <v>1.834</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5133</v>
+        <v>-0.4933</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6932</v>
+        <v>0.3001</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2875</v>
+        <v>1.0069</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4057</v>
+        <v>-0.7068</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9833</v>
+        <v>1.0407</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8757</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1076</v>
+        <v>0.2136</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5805</v>
+        <v>1.4117</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5239</v>
+        <v>0.9614</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0566</v>
+        <v>0.4503</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5637</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3424</v>
+        <v>-3.7836</v>
       </c>
       <c r="F20" t="n">
-        <v>3.7787</v>
+        <v>3.717</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1168</v>
@@ -2014,13 +2014,13 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9472</v>
+        <v>-0.45</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3014</v>
+        <v>-0.7426</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3542</v>
+        <v>0.2926</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3698</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7395</v>
+        <v>-1.3274</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0215</v>
+        <v>-1.0306</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.718</v>
+        <v>-0.2968</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4665</v>
+        <v>1.5788</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.523</v>
+        <v>0.9063</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0566</v>
+        <v>0.6725</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9756</v>
+        <v>0.9342</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0521</v>
+        <v>0.8577</v>
       </c>
       <c r="L21" t="n">
         <v>0.0765</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5091</v>
+        <v>0.6446</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5291</v>
+        <v>0.0486</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0199</v>
+        <v>0.596</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8994</v>
+        <v>0.289</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9542</v>
+        <v>0.2103</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9452</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.8249</v>
+        <v>-1.8902</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.8249</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2915</v>
+        <v>-1.5333</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2209</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0706</v>
+        <v>-0.8413</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8998</v>
+        <v>-0.4665</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8607</v>
+        <v>-0.523</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0391</v>
+        <v>0.0566</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5461</v>
+        <v>-0.9756</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3166</v>
+        <v>-1.0521</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2295</v>
+        <v>0.0765</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3538</v>
+        <v>0.5091</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5442</v>
+        <v>0.5291</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8096</v>
+        <v>-0.0199</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2209</v>
+        <v>1.1056</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0601</v>
+        <v>0.2836</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1608</v>
+        <v>0.822</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.1947</v>
+        <v>-2.8249</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4552</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4777</v>
+        <v>-1.6884</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3658</v>
+        <v>-1.5562</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1119</v>
+        <v>-0.1323</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5788</v>
+        <v>1.8998</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9063</v>
+        <v>0.8607</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6725</v>
+        <v>1.0391</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9342</v>
+        <v>0.5461</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8577</v>
+        <v>0.3166</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0765</v>
+        <v>0.2295</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6446</v>
+        <v>1.3538</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0486</v>
+        <v>0.5442</v>
       </c>
       <c r="O23" t="n">
-        <v>0.596</v>
+        <v>0.8096</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1387</v>
+        <v>-0.1761</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.125</v>
+        <v>-0.2752</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2636</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8902</v>
+        <v>-3.1947</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8902</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6699</v>
+        <v>-3.7181</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8088</v>
+        <v>-2.7029</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8611</v>
+        <v>-1.0152</v>
       </c>
       <c r="G24" t="n">
         <v>0.8368</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3633</v>
+        <v>0.3151</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2281</v>
+        <v>0.3341</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1352</v>
+        <v>-0.0189</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2599</v>
@@ -2362,7 +2362,7 @@
         <v>17.0597</v>
       </c>
       <c r="E25" t="n">
-        <v>1.993400000000001</v>
+        <v>1.993299999999999</v>
       </c>
       <c r="F25" t="n">
         <v>15.0661</v>
@@ -2392,7 +2392,7 @@
         <v>5.6092</v>
       </c>
       <c r="O25" t="n">
-        <v>6.9287</v>
+        <v>6.928699999999999</v>
       </c>
       <c r="P25" t="n">
         <v>-1.0875</v>
@@ -2407,10 +2407,10 @@
         <v>3.9476</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.02389999999999981</v>
+        <v>-0.02389999999999987</v>
       </c>
       <c r="U25" t="n">
-        <v>3.9714</v>
+        <v>3.9715</v>
       </c>
       <c r="V25" t="n">
         <v>-11.1252</v>
